--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/workout-session-schema/workoutSessionExercisesUpdateSchema-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/workout-session-schema/workoutSessionExercisesUpdateSchema-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="129">
-  <si>
-    <t>Statement: workoutSessionExercisesUpdateSchema – validate the array of exercises when updating a session.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="160">
+  <si>
+    <t>Statement: workoutSessionExercisesUpdateSchema – Validates an array of workout session exercise entries for an update operation using Zod safeParse. Identical to workoutSessionExercisesSchema except each entry may optionally include an id field. Returns { success: true, data } when the array contains at least one entry and every entry satisfies its field constraints. Returns { success: false, error } when the array is empty or any entry violates a constraint. Array constraints: minimum length 1. Per-entry constraints: id is optional (when present, any non-empty string is accepted). exerciseId is required (at least 1 character after trimming, not whitespace-only; surrounding whitespace trimmed). sets is required and must be an integer in the range 0–6 inclusive. reps is required and must be an integer in the range 0–30 inclusive. weight is required and must be a number in the range 0.0–500.0 inclusive.</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: Array&lt;{ id?: string, exerciseId: string, sets: number, reps: number, weight: number }&gt;</t>
+    <t>Input: Array&lt;WorkoutSessionExerciseUpdateInput { id?: string, exerciseId: string, sets: number, reps: number, weight: number }&gt;</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>Same as workoutSessionExercisesSchema + optional id field.</t>
+    <t>Input is passed directly to workoutSessionExercisesUpdateSchema.safeParse(). Array must contain at least 1 entry. Per entry: id is optional. exerciseId is required, at least 1 character after trim, not whitespace-only, surrounding whitespace trimmed. sets: required, integer, 0 ≤ sets ≤ 6. reps: required, integer, 0 ≤ reps ≤ 30. weight: required, number, 0.0 ≤ weight ≤ 500.0.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: { success: true, data } OR { success: false, error }</t>
+    <t>Output: { success: boolean, data?: WorkoutSessionExerciseUpdateInput[], error?: ZodError }</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>Validation results match constraints.</t>
+    <t>On success: parsed data is an array of entries with exerciseId trimmed; id is present when supplied. On failure: error.issues[0].path contains the name of the offending field.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,34 +64,31 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>Exercise without ID</t>
-  </si>
-  <si>
-    <t>Valid entry</t>
-  </si>
-  <si>
-    <t>Exercise with ID</t>
-  </si>
-  <si>
-    <t>Empty array</t>
-  </si>
-  <si>
-    <t>Length=0</t>
-  </si>
-  <si>
-    <t>ExerciseId presence</t>
-  </si>
-  <si>
-    <t>Present</t>
-  </si>
-  <si>
-    <t>Missing</t>
-  </si>
-  <si>
-    <t>ExerciseId whitespace</t>
-  </si>
-  <si>
-    <t>Surrounding whitespace</t>
+    <t>id field presence</t>
+  </si>
+  <si>
+    <t>Entry without id field (id omitted) → success: true, parsed data matches the input</t>
+  </si>
+  <si>
+    <t>Entry with id: "uuid-123" (id present) → success: true, parsed entry id is "uuid-123"</t>
+  </si>
+  <si>
+    <t>Array length</t>
+  </si>
+  <si>
+    <t>Empty array [] → success: false</t>
+  </si>
+  <si>
+    <t>exerciseId presence</t>
+  </si>
+  <si>
+    <t>Entry with exerciseId field absent → success: false, error path contains "exerciseId"</t>
+  </si>
+  <si>
+    <t>exerciseId whitespace</t>
+  </si>
+  <si>
+    <t>Entry with exerciseId: "  exercise-123  " (surrounding whitespace) → success: true, parsed exerciseId is "exercise-123"</t>
   </si>
   <si>
     <t>No TC</t>
@@ -112,10 +109,10 @@
     <t>EC-1</t>
   </si>
   <si>
-    <t>Valid entry without ID</t>
-  </si>
-  <si>
-    <t>success: true</t>
+    <t>array containing one entry with all fields valid and no id field: exerciseId "exercise-123", sets 3, reps 10, weight 80.5</t>
+  </si>
+  <si>
+    <t>success: true, parsed data matches the input</t>
   </si>
   <si>
     <t>Passed</t>
@@ -124,13 +121,16 @@
     <t>EC-2</t>
   </si>
   <si>
-    <t>Valid entry with ID</t>
+    <t>array containing one entry with all fields valid and id: "uuid-123": exerciseId "exercise-123", sets 3, reps 10, weight 80.5</t>
+  </si>
+  <si>
+    <t>success: true, parsed entry id is "uuid-123"</t>
   </si>
   <si>
     <t>EC-3</t>
   </si>
   <si>
-    <t>[] (empty array)</t>
+    <t>empty array []</t>
   </si>
   <si>
     <t>success: false</t>
@@ -139,13 +139,19 @@
     <t>EC-4</t>
   </si>
   <si>
-    <t>Missing exerciseId field</t>
+    <t>array with one entry where exerciseId field is absent: { sets: 3, reps: 10, weight: 80.5 }</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "exerciseId"</t>
   </si>
   <si>
     <t>EC-5</t>
   </si>
   <si>
-    <t>exerciseId="  exercise-123  "</t>
+    <t>array with one entry where exerciseId: "  exercise-123  " (surrounding whitespace)</t>
+  </si>
+  <si>
+    <t>success: true, parsed exerciseId is "exercise-123"</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -154,178 +160,238 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>Sets range</t>
-  </si>
-  <si>
-    <t>-1 (Below Min)</t>
-  </si>
-  <si>
-    <t>0 (At Min)</t>
-  </si>
-  <si>
-    <t>1 (Above Min)</t>
-  </si>
-  <si>
-    <t>5 (Below Max)</t>
-  </si>
-  <si>
-    <t>6 (At Max)</t>
-  </si>
-  <si>
-    <t>7 (Above Max)</t>
-  </si>
-  <si>
-    <t>Reps range</t>
-  </si>
-  <si>
-    <t>29 (Below Max)</t>
-  </si>
-  <si>
-    <t>30 (At Max)</t>
-  </si>
-  <si>
-    <t>31 (Above Max)</t>
-  </si>
-  <si>
-    <t>Weight range</t>
-  </si>
-  <si>
-    <t>-0.1 (Below Min)</t>
-  </si>
-  <si>
-    <t>0.0 (At Min)</t>
-  </si>
-  <si>
-    <t>0.1 (Above Min)</t>
-  </si>
-  <si>
-    <t>499.9 (Below Max)</t>
-  </si>
-  <si>
-    <t>500.0 (At Max)</t>
-  </si>
-  <si>
-    <t>500.1 (Above Max)</t>
-  </si>
-  <si>
-    <t>1 char padded</t>
+    <t>sets range</t>
+  </si>
+  <si>
+    <t>sets: -1 (min - 1): below minimum → success: false</t>
+  </si>
+  <si>
+    <t>sets: 0 (min): at minimum → success: true, parsed sets is 0</t>
+  </si>
+  <si>
+    <t>sets: 1 (min + 1): above minimum → success: true, parsed sets is 1</t>
+  </si>
+  <si>
+    <t>sets: 5 (max - 1): below maximum → success: true, parsed sets is 5</t>
+  </si>
+  <si>
+    <t>sets: 6 (max): at maximum → success: true, parsed sets is 6</t>
+  </si>
+  <si>
+    <t>sets: 7 (max + 1): above maximum → success: false</t>
+  </si>
+  <si>
+    <t>reps range</t>
+  </si>
+  <si>
+    <t>reps: -1 (min - 1): below minimum → success: false</t>
+  </si>
+  <si>
+    <t>reps: 0 (min): at minimum → success: true, parsed reps is 0</t>
+  </si>
+  <si>
+    <t>reps: 1 (min + 1): above minimum → success: true, parsed reps is 1</t>
+  </si>
+  <si>
+    <t>reps: 29 (max - 1): below maximum → success: true, parsed reps is 29</t>
+  </si>
+  <si>
+    <t>reps: 30 (max): at maximum → success: true, parsed reps is 30</t>
+  </si>
+  <si>
+    <t>reps: 31 (max + 1): above maximum → success: false</t>
+  </si>
+  <si>
+    <t>weight range</t>
+  </si>
+  <si>
+    <t>weight: -0.1 (min - 0.1): below minimum → success: false</t>
+  </si>
+  <si>
+    <t>weight: 0.0 (min): at minimum → success: true, parsed weight is 0</t>
+  </si>
+  <si>
+    <t>weight: 0.1 (min + 0.1): above minimum → success: true, parsed weight is 0.1</t>
+  </si>
+  <si>
+    <t>weight: 499.9 (max - 0.1): below maximum → success: true, parsed weight is 499.9</t>
+  </si>
+  <si>
+    <t>weight: 500.0 (max): at maximum → success: true, parsed weight is 500</t>
+  </si>
+  <si>
+    <t>weight: 500.1 (max + 0.1): above maximum → success: false</t>
+  </si>
+  <si>
+    <t>exerciseId whitespace + trim</t>
+  </si>
+  <si>
+    <t>exerciseId: " E " (1 real character after trim, at minimum) → success: true, parsed exerciseId is "E"</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1 Sets -1</t>
-  </si>
-  <si>
-    <t>sets=-1</t>
-  </si>
-  <si>
-    <t>BVA-1 Sets 0</t>
-  </si>
-  <si>
-    <t>sets=0</t>
-  </si>
-  <si>
-    <t>BVA-1 Sets 1</t>
-  </si>
-  <si>
-    <t>sets=1</t>
-  </si>
-  <si>
-    <t>BVA-1 Sets 5</t>
-  </si>
-  <si>
-    <t>sets=5</t>
-  </si>
-  <si>
-    <t>BVA-1 Sets 6</t>
-  </si>
-  <si>
-    <t>sets=6</t>
-  </si>
-  <si>
-    <t>BVA-1 Sets 7</t>
-  </si>
-  <si>
-    <t>sets=7</t>
-  </si>
-  <si>
-    <t>BVA-2 Reps -1</t>
-  </si>
-  <si>
-    <t>reps=-1</t>
-  </si>
-  <si>
-    <t>BVA-2 Reps 0</t>
-  </si>
-  <si>
-    <t>reps=0</t>
-  </si>
-  <si>
-    <t>BVA-2 Reps 1</t>
-  </si>
-  <si>
-    <t>reps=1</t>
-  </si>
-  <si>
-    <t>BVA-2 Reps 29</t>
-  </si>
-  <si>
-    <t>reps=29</t>
-  </si>
-  <si>
-    <t>BVA-2 Reps 30</t>
-  </si>
-  <si>
-    <t>reps=30</t>
-  </si>
-  <si>
-    <t>BVA-2 Reps 31</t>
-  </si>
-  <si>
-    <t>reps=31</t>
-  </si>
-  <si>
-    <t>BVA-3 Weight -0.1</t>
-  </si>
-  <si>
-    <t>weight=-0.1</t>
-  </si>
-  <si>
-    <t>BVA-3 Weight 0</t>
-  </si>
-  <si>
-    <t>weight=0</t>
-  </si>
-  <si>
-    <t>BVA-3 Weight 0.1</t>
-  </si>
-  <si>
-    <t>weight=0.1</t>
-  </si>
-  <si>
-    <t>BVA-3 Weight 499.9</t>
-  </si>
-  <si>
-    <t>weight=499.9</t>
-  </si>
-  <si>
-    <t>BVA-3 Weight 500</t>
-  </si>
-  <si>
-    <t>weight=500</t>
-  </si>
-  <si>
-    <t>BVA-3 Weight 500.1</t>
-  </si>
-  <si>
-    <t>weight=500.1</t>
-  </si>
-  <si>
-    <t>BVA-4 ExerciseId padded</t>
-  </si>
-  <si>
-    <t>exerciseId=" E "</t>
+    <t>BVA-1  (sets=-1)</t>
+  </si>
+  <si>
+    <t>array with one entry where sets: -1</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "sets"</t>
+  </si>
+  <si>
+    <t>BVA-2  (sets=0)</t>
+  </si>
+  <si>
+    <t>array with one entry where sets: 0</t>
+  </si>
+  <si>
+    <t>success: true, parsed sets is 0</t>
+  </si>
+  <si>
+    <t>BVA-3  (sets=1)</t>
+  </si>
+  <si>
+    <t>array with one entry where sets: 1</t>
+  </si>
+  <si>
+    <t>success: true, parsed sets is 1</t>
+  </si>
+  <si>
+    <t>BVA-4  (sets=5)</t>
+  </si>
+  <si>
+    <t>array with one entry where sets: 5</t>
+  </si>
+  <si>
+    <t>success: true, parsed sets is 5</t>
+  </si>
+  <si>
+    <t>BVA-5  (sets=6)</t>
+  </si>
+  <si>
+    <t>array with one entry where sets: 6</t>
+  </si>
+  <si>
+    <t>success: true, parsed sets is 6</t>
+  </si>
+  <si>
+    <t>BVA-6  (sets=7)</t>
+  </si>
+  <si>
+    <t>array with one entry where sets: 7</t>
+  </si>
+  <si>
+    <t>BVA-7  (reps=-1)</t>
+  </si>
+  <si>
+    <t>array with one entry where reps: -1</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "reps"</t>
+  </si>
+  <si>
+    <t>BVA-8  (reps=0)</t>
+  </si>
+  <si>
+    <t>array with one entry where reps: 0</t>
+  </si>
+  <si>
+    <t>success: true, parsed reps is 0</t>
+  </si>
+  <si>
+    <t>BVA-9  (reps=1)</t>
+  </si>
+  <si>
+    <t>array with one entry where reps: 1</t>
+  </si>
+  <si>
+    <t>success: true, parsed reps is 1</t>
+  </si>
+  <si>
+    <t>BVA-10 (reps=29)</t>
+  </si>
+  <si>
+    <t>array with one entry where reps: 29</t>
+  </si>
+  <si>
+    <t>success: true, parsed reps is 29</t>
+  </si>
+  <si>
+    <t>BVA-11 (reps=30)</t>
+  </si>
+  <si>
+    <t>array with one entry where reps: 30</t>
+  </si>
+  <si>
+    <t>success: true, parsed reps is 30</t>
+  </si>
+  <si>
+    <t>BVA-12 (reps=31)</t>
+  </si>
+  <si>
+    <t>array with one entry where reps: 31</t>
+  </si>
+  <si>
+    <t>BVA-13 (wt=-0.1)</t>
+  </si>
+  <si>
+    <t>array with one entry where weight: -0.1</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "weight"</t>
+  </si>
+  <si>
+    <t>BVA-14 (wt=0)</t>
+  </si>
+  <si>
+    <t>array with one entry where weight: 0</t>
+  </si>
+  <si>
+    <t>success: true, parsed weight is 0</t>
+  </si>
+  <si>
+    <t>BVA-15 (wt=0.1)</t>
+  </si>
+  <si>
+    <t>array with one entry where weight: 0.1</t>
+  </si>
+  <si>
+    <t>success: true, parsed weight is 0.1</t>
+  </si>
+  <si>
+    <t>BVA-16 (wt=499.9)</t>
+  </si>
+  <si>
+    <t>array with one entry where weight: 499.9</t>
+  </si>
+  <si>
+    <t>success: true, parsed weight is 499.9</t>
+  </si>
+  <si>
+    <t>BVA-17 (wt=500)</t>
+  </si>
+  <si>
+    <t>array with one entry where weight: 500</t>
+  </si>
+  <si>
+    <t>success: true, parsed weight is 500</t>
+  </si>
+  <si>
+    <t>BVA-18 (wt=500.1)</t>
+  </si>
+  <si>
+    <t>array with one entry where weight: 500.1</t>
+  </si>
+  <si>
+    <t>BVA-19 (pad→1)</t>
+  </si>
+  <si>
+    <t>array with one entry where exerciseId: " E " (1 real character after trim)</t>
+  </si>
+  <si>
+    <t>success: true, parsed exerciseId is "E"</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -334,21 +400,6 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>Valid update entry without ID</t>
-  </si>
-  <si>
-    <t>Valid update entry with ID</t>
-  </si>
-  <si>
-    <t>Empty array []</t>
-  </si>
-  <si>
-    <t>Entry missing exerciseId</t>
-  </si>
-  <si>
-    <t>ExerciseId with surrounding whitespace</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
@@ -361,7 +412,49 @@
     <t>BVA-4</t>
   </si>
   <si>
-    <t>exerciseId 1 char padded with whitespace</t>
+    <t>BVA-5</t>
+  </si>
+  <si>
+    <t>BVA-6</t>
+  </si>
+  <si>
+    <t>BVA-7</t>
+  </si>
+  <si>
+    <t>BVA-8</t>
+  </si>
+  <si>
+    <t>BVA-9</t>
+  </si>
+  <si>
+    <t>BVA-10</t>
+  </si>
+  <si>
+    <t>BVA-11</t>
+  </si>
+  <si>
+    <t>BVA-12</t>
+  </si>
+  <si>
+    <t>BVA-13</t>
+  </si>
+  <si>
+    <t>BVA-14</t>
+  </si>
+  <si>
+    <t>BVA-15</t>
+  </si>
+  <si>
+    <t>BVA-16</t>
+  </si>
+  <si>
+    <t>BVA-17</t>
+  </si>
+  <si>
+    <t>BVA-18</t>
+  </si>
+  <si>
+    <t>BVA-19</t>
   </si>
   <si>
     <t>Testing</t>
@@ -394,7 +487,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>WSM-07</t>
+    <t>SCHEMA-12</t>
   </si>
   <si>
     <t>n/a</t>
@@ -960,10 +1053,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>1</v>
@@ -991,10 +1084,10 @@
         <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1002,10 +1095,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>1</v>
@@ -1031,19 +1124,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1051,16 +1144,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="E2" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1068,16 +1161,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="E3" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1094,7 +1187,7 @@
         <v>38</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1108,10 +1201,10 @@
         <v>40</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1119,16 +1212,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1149,13 +1242,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1163,208 +1256,208 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
+      <c r="A3" s="1">
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
+      <c r="A5" s="1">
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>1</v>
+      <c r="A6" s="1">
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>1</v>
+      <c r="A7" s="1">
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>1</v>
+      <c r="A9" s="1">
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>1</v>
+      <c r="A10" s="1">
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>1</v>
+      <c r="A11" s="1">
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>1</v>
+      <c r="A12" s="1">
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="13" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="C13" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>1</v>
+      <c r="A15" s="1">
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>1</v>
+      <c r="A16" s="1">
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>1</v>
+      <c r="A17" s="1">
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>1</v>
+      <c r="A18" s="1">
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="19" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="C19" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1387,19 +1480,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1407,16 +1500,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1424,16 +1517,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1441,16 +1534,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1458,16 +1551,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1475,16 +1568,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1492,16 +1585,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1509,16 +1602,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1526,16 +1619,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1543,16 +1636,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1560,16 +1653,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1577,16 +1670,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1594,16 +1687,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1611,16 +1704,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1628,16 +1721,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1645,16 +1738,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>32</v>
+        <v>113</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1662,16 +1755,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1679,16 +1772,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1696,16 +1789,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1713,16 +1806,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>32</v>
+        <v>124</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1746,22 +1839,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1769,19 +1862,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1789,19 +1882,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1815,13 +1908,13 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>107</v>
+        <v>37</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1835,13 +1928,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1849,19 +1942,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>109</v>
+        <v>43</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1872,16 +1965,16 @@
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1892,16 +1985,16 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1912,16 +2005,16 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1932,16 +2025,16 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1952,16 +2045,16 @@
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1972,16 +2065,16 @@
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1992,16 +2085,16 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2012,16 +2105,16 @@
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2032,16 +2125,16 @@
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2052,16 +2145,16 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2072,16 +2165,16 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2092,16 +2185,16 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2112,16 +2205,16 @@
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2132,16 +2225,16 @@
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2152,16 +2245,16 @@
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="E21" s="1" t="s">
-        <v>32</v>
+        <v>113</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2172,16 +2265,16 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2192,16 +2285,16 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2212,16 +2305,16 @@
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2232,16 +2325,16 @@
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>32</v>
+        <v>124</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -2269,16 +2362,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -2286,39 +2379,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>124</v>
+        <v>155</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="B3" s="1">
         <v>24</v>
@@ -2333,19 +2426,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>127</v>
+        <v>158</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/workout-session-schema/workoutSessionExercisesUpdateSchema-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/workout-session-schema/workoutSessionExercisesUpdateSchema-bbt-form.xlsx
@@ -487,7 +487,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SCHEMA-12</t>
+    <t>SCHEMA-14</t>
   </si>
   <si>
     <t>n/a</t>

--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/workout-session-schema/workoutSessionExercisesUpdateSchema-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/workout-session-schema/workoutSessionExercisesUpdateSchema-bbt-form.xlsx
@@ -487,7 +487,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SCHEMA-14</t>
+    <t>SCHEMA-16</t>
   </si>
   <si>
     <t>n/a</t>
